--- a/OUTPUT/gate_oof/fold_4/expert_inner_metrics.xlsx
+++ b/OUTPUT/gate_oof/fold_4/expert_inner_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,10 +535,10 @@
         <v>460</v>
       </c>
       <c r="H2" t="n">
-        <v>4.36396269999932</v>
+        <v>2.678861899999902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.044062799999665</v>
+        <v>0.02908970002317801</v>
       </c>
       <c r="J2" t="n">
         <v>0.003515297875341661</v>
@@ -587,31 +587,31 @@
         <v>752</v>
       </c>
       <c r="H3" t="n">
-        <v>11.21557550000034</v>
+        <v>6.928101200028323</v>
       </c>
       <c r="I3" t="n">
-        <v>1.127776600000288</v>
+        <v>0.5368101000203751</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005897740631610783</v>
+        <v>0.005907007994491202</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004294757274524213</v>
+        <v>0.004302530334483916</v>
       </c>
       <c r="L3" t="n">
-        <v>0.683638112671386</v>
+        <v>0.6826431065985497</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4473526852218452</v>
+        <v>0.4481559626681163</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0003462279130315036</v>
+        <v>-0.0003418042249745058</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01277460325715364</v>
+        <v>0.01280981818844832</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02219007013556273</v>
+        <v>0.02290516274175902</v>
       </c>
     </row>
     <row r="4">
@@ -639,31 +639,31 @@
         <v>1443</v>
       </c>
       <c r="H4" t="n">
-        <v>22.59217759999956</v>
+        <v>9.911988099978771</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9038379000012355</v>
+        <v>0.6930584000074305</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005369706140804752</v>
+        <v>0.005367865067399092</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004117952126307878</v>
+        <v>0.00411870855781453</v>
       </c>
       <c r="L4" t="n">
-        <v>0.609900347984385</v>
+        <v>0.6101678035782669</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4174898115860646</v>
+        <v>0.4175709401354895</v>
       </c>
       <c r="N4" t="n">
-        <v>6.875595008257598e-05</v>
+        <v>7.079039251820899e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01104547658103548</v>
+        <v>0.01107995743192842</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01863726183452252</v>
+        <v>0.01863653503266105</v>
       </c>
     </row>
     <row r="5">
@@ -691,10 +691,10 @@
         <v>460</v>
       </c>
       <c r="H5" t="n">
-        <v>6.606010699999388</v>
+        <v>2.182912099990062</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08327059999828634</v>
+        <v>0.02041930000996217</v>
       </c>
       <c r="J5" t="n">
         <v>0.00353271717912654</v>
@@ -743,31 +743,31 @@
         <v>752</v>
       </c>
       <c r="H6" t="n">
-        <v>12.99583350000103</v>
+        <v>4.764197000011336</v>
       </c>
       <c r="I6" t="n">
-        <v>1.122360499999559</v>
+        <v>0.6063696999917738</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00556964160466881</v>
+        <v>0.005567122794421997</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004003320951249367</v>
+        <v>0.004010264280711369</v>
       </c>
       <c r="L6" t="n">
-        <v>0.71764016299011</v>
+        <v>0.7178954936136968</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4169631247379256</v>
+        <v>0.4177029996266461</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0003620460011250552</v>
+        <v>-0.0003624806224695665</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01189485524959435</v>
+        <v>0.01171593715249609</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02265833707423515</v>
+        <v>0.02264613977268159</v>
       </c>
     </row>
     <row r="7">
@@ -795,31 +795,31 @@
         <v>1443</v>
       </c>
       <c r="H7" t="n">
-        <v>23.07276610000008</v>
+        <v>10.52075750002405</v>
       </c>
       <c r="I7" t="n">
-        <v>1.614817699999548</v>
+        <v>12.9466276000021</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005187626552135251</v>
+        <v>0.005198581488217491</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004031394919224655</v>
+        <v>0.004040064308545537</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6264288384245398</v>
+        <v>0.6248493996363889</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4086402464251202</v>
+        <v>0.4095074736199015</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.941464612624467e-06</v>
+        <v>-2.104082963972945e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009975145087729599</v>
+        <v>0.01003232426079609</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01921816775731755</v>
+        <v>0.01923760087257231</v>
       </c>
     </row>
     <row r="8">
@@ -847,10 +847,10 @@
         <v>460</v>
       </c>
       <c r="H8" t="n">
-        <v>9.661398800000825</v>
+        <v>11.3894473000546</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05849680000028457</v>
+        <v>0.04917499999282882</v>
       </c>
       <c r="J8" t="n">
         <v>0.003611124287304238</v>
@@ -899,31 +899,31 @@
         <v>752</v>
       </c>
       <c r="H9" t="n">
-        <v>11.74272620000011</v>
+        <v>15.4680636000121</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9698077000011835</v>
+        <v>1.844508800015319</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005075803754139072</v>
+        <v>0.00506434940396621</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003710503488939203</v>
+        <v>0.00369513076304691</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7619235831185867</v>
+        <v>0.7629968845362159</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3866434571629015</v>
+        <v>0.3850319189881092</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0001416128748404718</v>
+        <v>-0.0001403900769417501</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01053665487432871</v>
+        <v>0.01042305507816695</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02410407230232159</v>
+        <v>0.02349423225992475</v>
       </c>
     </row>
     <row r="10">
@@ -951,31 +951,31 @@
         <v>1442</v>
       </c>
       <c r="H10" t="n">
-        <v>23.16047950000029</v>
+        <v>33.20567049999954</v>
       </c>
       <c r="I10" t="n">
-        <v>1.232191300001432</v>
+        <v>2.006897000013851</v>
       </c>
       <c r="J10" t="n">
-        <v>0.005323352057238077</v>
+        <v>0.005334011568558693</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004056013928262144</v>
+        <v>0.004063292049244091</v>
       </c>
       <c r="L10" t="n">
-        <v>0.612701385866623</v>
+        <v>0.6111487749186636</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4113421578468405</v>
+        <v>0.4120921991549944</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0002079600421481269</v>
+        <v>0.0002217824783177473</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01096622947270511</v>
+        <v>0.01100842198843157</v>
       </c>
       <c r="P10" t="n">
-        <v>0.019768671847192</v>
+        <v>0.01967476116049116</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +1003,10 @@
         <v>460</v>
       </c>
       <c r="H11" t="n">
-        <v>17.26134660000025</v>
+        <v>51.58860580000328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05956619999960822</v>
+        <v>0.0628038999857381</v>
       </c>
       <c r="J11" t="n">
         <v>0.003543360491592642</v>
@@ -1055,31 +1055,31 @@
         <v>751</v>
       </c>
       <c r="H12" t="n">
-        <v>14.06743649999953</v>
+        <v>64.71126910002204</v>
       </c>
       <c r="I12" t="n">
-        <v>1.33379739999873</v>
+        <v>2.706326599989552</v>
       </c>
       <c r="J12" t="n">
-        <v>0.005787665785552847</v>
+        <v>0.005790359039438901</v>
       </c>
       <c r="K12" t="n">
-        <v>0.003968769687395245</v>
+        <v>0.00397137007044658</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6845952562767421</v>
+        <v>0.6843016447484316</v>
       </c>
       <c r="M12" t="n">
-        <v>0.413465312223929</v>
+        <v>0.4137481806458176</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0003309111901286941</v>
+        <v>-0.0003170511327430966</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01212428518567016</v>
+        <v>0.01223097535238116</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02587210334376921</v>
+        <v>0.02601154068047218</v>
       </c>
     </row>
     <row r="13">
@@ -1107,31 +1107,31 @@
         <v>1442</v>
       </c>
       <c r="H13" t="n">
-        <v>26.52447660000144</v>
+        <v>67.00239750003675</v>
       </c>
       <c r="I13" t="n">
-        <v>1.578035099999397</v>
+        <v>0.5780533000361174</v>
       </c>
       <c r="J13" t="n">
-        <v>0.005503472119077807</v>
+        <v>0.005505028987522679</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004115172154339565</v>
+        <v>0.004121040071259669</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5852953763561333</v>
+        <v>0.5850607129107179</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4172529519425045</v>
+        <v>0.4178330509836517</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0001626692523669012</v>
+        <v>0.0001501047732801227</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01163954706086551</v>
+        <v>0.01170259730263182</v>
       </c>
       <c r="P13" t="n">
-        <v>0.02504498642010733</v>
+        <v>0.02514427238608252</v>
       </c>
     </row>
     <row r="14">
@@ -1159,10 +1159,10 @@
         <v>460</v>
       </c>
       <c r="H14" t="n">
-        <v>7.21545850000075</v>
+        <v>2.61706730001606</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07577049999963492</v>
+        <v>0.01960790000157431</v>
       </c>
       <c r="J14" t="n">
         <v>0.003421559369957159</v>
@@ -1211,31 +1211,31 @@
         <v>751</v>
       </c>
       <c r="H15" t="n">
-        <v>11.40606059999845</v>
+        <v>5.704732300015166</v>
       </c>
       <c r="I15" t="n">
-        <v>1.218235000000277</v>
+        <v>0.6800094000063837</v>
       </c>
       <c r="J15" t="n">
-        <v>0.005688879735341437</v>
+        <v>0.005682288563132585</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00409405462361163</v>
+        <v>0.004086217762079016</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7010198056489569</v>
+        <v>0.7017122050131337</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4270865825071203</v>
+        <v>0.4262576750032198</v>
       </c>
       <c r="N15" t="n">
-        <v>3.289009759067088e-05</v>
+        <v>2.059081815079687e-05</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01191243638199579</v>
+        <v>0.01189113005303161</v>
       </c>
       <c r="P15" t="n">
-        <v>0.02681444925885879</v>
+        <v>0.02663063214557781</v>
       </c>
     </row>
     <row r="16">
@@ -1263,31 +1263,31 @@
         <v>1442</v>
       </c>
       <c r="H16" t="n">
-        <v>21.41232300000047</v>
+        <v>14.16014330001781</v>
       </c>
       <c r="I16" t="n">
-        <v>1.153882800001156</v>
+        <v>0.456337200012058</v>
       </c>
       <c r="J16" t="n">
-        <v>0.005399218093890009</v>
+        <v>0.005390287386756053</v>
       </c>
       <c r="K16" t="n">
-        <v>0.004144723801378057</v>
+        <v>0.004130706614960789</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5992205159451365</v>
+        <v>0.6005452574049299</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4201431466915809</v>
+        <v>0.4187219544008295</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.511548495665253e-05</v>
+        <v>-5.738851142382549e-05</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01084755108564345</v>
+        <v>0.01086023387180421</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02015811903891296</v>
+        <v>0.0207407036350975</v>
       </c>
     </row>
   </sheetData>
